--- a/Links.xlsx
+++ b/Links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Documents/Profissional/Softwares/R (site)/CienciaComRConsultoria/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D8E440-48D9-7642-9C29-916D56B6B419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75E2B44-04FD-DC43-8A65-2470874A4891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="2" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
+    <workbookView xWindow="1080" yWindow="680" windowWidth="27600" windowHeight="17140" activeTab="3" xr2:uid="{F123CA71-A1F8-7C47-BA09-37F4DB1DDBA0}"/>
   </bookViews>
   <sheets>
     <sheet name="curriculo" sheetId="2" r:id="rId1"/>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="915">
   <si>
     <t>Doutorado</t>
   </si>
@@ -2647,9 +2647,6 @@
   </si>
   <si>
     <t>10.1097/phm.0000000000002932</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1hBNi-HHumKXb5lKH2V9XVpq5MTBxyXOY</t>
   </si>
   <si>
     <t>10.47066/2966-4837.e00072025en</t>
@@ -2877,6 +2874,27 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1nXGc5lEOge5avTjvbtyuii8sTHDoWsc2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WYSK6p4JAZ7q9S789t0K4RdOCGs2VSLy</t>
+  </si>
+  <si>
+    <t>10.1016/j.aanat.2026.153067</t>
+  </si>
+  <si>
+    <t>Soundararajan, L. R. A., Thankappan, S. M., Ferreira, A. D. S., Lemos, T., &amp; Almeida, R. (2026). Influence of Minimalist Footwear on Intrinsic Foot Muscle Characteristics, Arch Integrity, and Foot Function: A Systematic Review Protocol. Annals of Anatomy - Anatomischer Anzeiger, 267, 153067. https://doi.org/10.1016/j.aanat.2026.153067</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jtOedl0LlKuUk6anyC7nGfC3iBqzKlxa</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1v_MwU5YSq8isnt60UbM9pSyBqmfEVd0y</t>
+  </si>
+  <si>
+    <t>10.2139/ssrn.7557206</t>
+  </si>
+  <si>
+    <t>Campello, Cesar Ricardo Simioni and Costa, Paula Ribeiro Quinet de Andra and Reis, Samia Najara Freitas Bessa and Silva, Acácia Pinheiro Alvares Ferna and Ferreira, Arthur de Sá, INTER-RATER AND INTRA-RATER RELIABILITY OF THE MODIFIED TARDIEU AND MRC SCALES IN CHILDREN WITH CEREBRAL PALSY.  http://dx.doi.org/10.2139/ssrn.7557206</t>
   </si>
 </sst>
 </file>
@@ -3480,7 +3498,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -5655,24 +5673,24 @@
     </row>
     <row r="191" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="C191" s="6" t="s">
         <v>885</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="B192" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="B192" s="7" t="s">
-        <v>839</v>
-      </c>
       <c r="C192" s="6" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="136" x14ac:dyDescent="0.2">
@@ -5820,7 +5838,7 @@
     </row>
     <row r="206" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>674</v>
@@ -5842,7 +5860,7 @@
     </row>
     <row r="208" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>731</v>
@@ -5886,35 +5904,35 @@
     </row>
     <row r="212" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>869</v>
+      </c>
+      <c r="C212" s="6" t="s">
         <v>868</v>
-      </c>
-      <c r="B212" s="17" t="s">
-        <v>870</v>
-      </c>
-      <c r="C212" s="6" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="153" x14ac:dyDescent="0.2">
@@ -5930,46 +5948,46 @@
     </row>
     <row r="216" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A217" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="C217" s="6" t="s">
         <v>897</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>899</v>
-      </c>
-      <c r="C217" s="6" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A218" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B218" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="C218" s="6" t="s">
         <v>861</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A219" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="C219" s="6" t="s">
         <v>906</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="C219" s="6" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="68" x14ac:dyDescent="0.2">
@@ -5985,87 +6003,87 @@
     </row>
     <row r="221" spans="1:3" ht="85" x14ac:dyDescent="0.2">
       <c r="A221" s="6" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A222" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="C222" s="6" t="s">
         <v>892</v>
-      </c>
-      <c r="B222" s="9" t="s">
-        <v>891</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A223" s="6" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B223" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="C223" s="6" t="s">
         <v>901</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="119" x14ac:dyDescent="0.2">
       <c r="A224" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="B224" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="C224" s="6" t="s">
         <v>854</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>856</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="170" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="C225" s="6" t="s">
         <v>879</v>
-      </c>
-      <c r="B225" s="9" t="s">
-        <v>881</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="187" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="B226" s="9" t="s">
         <v>895</v>
       </c>
-      <c r="B226" s="9" t="s">
-        <v>896</v>
-      </c>
       <c r="C226" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A227" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="221" x14ac:dyDescent="0.2">
       <c r="A228" s="6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>836</v>
+        <v>911</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>835</v>
@@ -6073,39 +6091,39 @@
     </row>
     <row r="229" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A229" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B229" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="C229" s="6" t="s">
         <v>874</v>
-      </c>
-      <c r="C229" s="6" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="136" x14ac:dyDescent="0.2">
       <c r="A230" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="C231" s="6" t="s">
         <v>845</v>
       </c>
-      <c r="B231" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="C231" s="6" t="s">
-        <v>846</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C187 C189:C1048576">
+  <conditionalFormatting sqref="C1:C187 C233:C1048576 C189:C231">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
@@ -6319,26 +6337,26 @@
     <hyperlink ref="B215" r:id="rId208" xr:uid="{DDB78A85-B6DB-7C44-8926-BCBA7584A870}"/>
     <hyperlink ref="B220" r:id="rId209" xr:uid="{5D951114-AC5B-764A-9248-B3AA437C0B38}"/>
     <hyperlink ref="B194" r:id="rId210" xr:uid="{F7EF741D-9590-8A41-A116-2F40CD601256}"/>
-    <hyperlink ref="B228" r:id="rId211" xr:uid="{9A85553B-9502-1A41-A6DA-49A2E77F4F92}"/>
-    <hyperlink ref="B192" r:id="rId212" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
-    <hyperlink ref="B221" r:id="rId213" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
-    <hyperlink ref="B231" r:id="rId214" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
-    <hyperlink ref="B224" r:id="rId215" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
-    <hyperlink ref="B227" r:id="rId216" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
-    <hyperlink ref="B218" r:id="rId217" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
-    <hyperlink ref="B214" r:id="rId218" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
-    <hyperlink ref="B212" r:id="rId219" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
-    <hyperlink ref="B230" r:id="rId220" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
-    <hyperlink ref="B229" r:id="rId221" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
-    <hyperlink ref="B213" r:id="rId222" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
-    <hyperlink ref="B225" r:id="rId223" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
-    <hyperlink ref="B216" r:id="rId224" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
-    <hyperlink ref="B191" r:id="rId225" xr:uid="{FD8B9A55-7C73-9841-A124-F2094F08EAEF}"/>
-    <hyperlink ref="B222" r:id="rId226" xr:uid="{F2FF60E7-6D7E-E943-807F-C28F2C324FD3}"/>
-    <hyperlink ref="B226" r:id="rId227" xr:uid="{9640ECC6-B685-EC43-A315-F7442ECD1C92}"/>
-    <hyperlink ref="B217" r:id="rId228" xr:uid="{CC131DE1-D6BE-5E48-AC48-287482CBE982}"/>
-    <hyperlink ref="B223" r:id="rId229" xr:uid="{21E33509-C69E-9C4B-BD46-34A01A62BAB0}"/>
-    <hyperlink ref="B219" r:id="rId230" xr:uid="{CF60C9D8-AC76-CA42-986C-91E7F2B11DC1}"/>
+    <hyperlink ref="B192" r:id="rId211" xr:uid="{6819F61D-1714-FC42-8465-B1A65C9986CE}"/>
+    <hyperlink ref="B221" r:id="rId212" xr:uid="{B7157666-F9CD-F34D-9B13-B1F2EB28E8E8}"/>
+    <hyperlink ref="B231" r:id="rId213" xr:uid="{E83FAF4B-DB22-274F-BCA3-C58C755BD58D}"/>
+    <hyperlink ref="B224" r:id="rId214" xr:uid="{2928D7C1-6775-A94C-84C0-1B7D86231939}"/>
+    <hyperlink ref="B227" r:id="rId215" xr:uid="{CFB8E14B-DC58-D24D-8E1C-FCE85A3B788D}"/>
+    <hyperlink ref="B218" r:id="rId216" xr:uid="{2EF4B64D-9E1E-1041-AB81-9E416919E974}"/>
+    <hyperlink ref="B214" r:id="rId217" xr:uid="{769F9F6C-56E8-1E40-A27E-8A66990CF537}"/>
+    <hyperlink ref="B212" r:id="rId218" xr:uid="{0DAA73AD-027B-FD4D-A704-91037FAB810E}"/>
+    <hyperlink ref="B230" r:id="rId219" xr:uid="{5288B60C-59AF-6441-A0AF-415C701A2005}"/>
+    <hyperlink ref="B229" r:id="rId220" xr:uid="{58570406-1DB7-8548-A875-E04FA60D4F39}"/>
+    <hyperlink ref="B213" r:id="rId221" xr:uid="{5444AD8E-4A7E-2541-9221-682B86429C04}"/>
+    <hyperlink ref="B225" r:id="rId222" xr:uid="{861A84FC-1D18-C94E-BB5C-E10908FFF174}"/>
+    <hyperlink ref="B216" r:id="rId223" xr:uid="{A286A8EB-8D50-D443-B19E-AA1245FA0243}"/>
+    <hyperlink ref="B191" r:id="rId224" xr:uid="{FD8B9A55-7C73-9841-A124-F2094F08EAEF}"/>
+    <hyperlink ref="B222" r:id="rId225" xr:uid="{F2FF60E7-6D7E-E943-807F-C28F2C324FD3}"/>
+    <hyperlink ref="B226" r:id="rId226" xr:uid="{9640ECC6-B685-EC43-A315-F7442ECD1C92}"/>
+    <hyperlink ref="B217" r:id="rId227" xr:uid="{CC131DE1-D6BE-5E48-AC48-287482CBE982}"/>
+    <hyperlink ref="B223" r:id="rId228" xr:uid="{21E33509-C69E-9C4B-BD46-34A01A62BAB0}"/>
+    <hyperlink ref="B219" r:id="rId229" xr:uid="{CF60C9D8-AC76-CA42-986C-91E7F2B11DC1}"/>
+    <hyperlink ref="B228" r:id="rId230" xr:uid="{683B6698-E1F2-5641-A745-EC2B23093D9D}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <legacyDrawing r:id="rId231"/>
@@ -6347,7 +6365,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA81A273-40D1-C043-B92A-150693AC55EB}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -6413,24 +6431,35 @@
     </row>
     <row r="6" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="102" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>849</v>
+    </row>
+    <row r="8" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -6444,9 +6473,10 @@
     <hyperlink ref="B5" r:id="rId4" xr:uid="{2C94C806-EACF-6D44-9C7E-30C52899A3FD}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{263172B8-675C-694E-B35C-A9767EC0337B}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{34713DE2-3C26-064D-8A48-31183CD24318}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{29DC9A4A-9636-C44E-B540-06EB81D2F7AF}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId7"/>
+  <legacyDrawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -6496,13 +6526,13 @@
     </row>
     <row r="4" spans="1:3" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -6671,7 +6701,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12814D52-B4A6-0C42-8333-C9B66CE67680}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43" style="6" customWidth="1"/>
@@ -7038,15 +7068,26 @@
         <v>777</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="119" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:3" ht="120" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>780</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="15" t="s">
         <v>766</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="14" t="s">
         <v>779</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -7090,9 +7131,10 @@
     <hyperlink ref="B35" r:id="rId34" xr:uid="{6FD89FF4-84D7-7B46-A2F8-B99283CD6FAD}"/>
     <hyperlink ref="B36" r:id="rId35" xr:uid="{79F6BA98-6E46-1F41-87EB-2D95927B5F93}"/>
     <hyperlink ref="B37" r:id="rId36" xr:uid="{A64B8C7F-6072-0745-AC8B-77DC954C66C2}"/>
+    <hyperlink ref="B38" r:id="rId37" xr:uid="{226620DF-6E94-0645-BE08-3C1E24C8FDB1}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId37"/>
+  <legacyDrawing r:id="rId38"/>
 </worksheet>
 </file>
 
@@ -7198,10 +7240,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
